--- a/asignaturas/BI/EXCEL/Miércoles 18 septiembre/Libro1.xlsx
+++ b/asignaturas/BI/EXCEL/Miércoles 18 septiembre/Libro1.xlsx
@@ -1,18 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20414"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAW\asignaturas\BI\EXCEL\Miércoles 18 septiembre\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4122F9-E94F-4707-AE5C-453364714D8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="IVA"/>
-    <sheet r:id="rId2" sheetId="2" name="Multiplicación"/>
-    <sheet r:id="rId3" sheetId="3" name="Descuentos"/>
-    <sheet r:id="rId4" sheetId="4" name="Hoja5"/>
+    <sheet name="IVA" sheetId="1" r:id="rId1"/>
+    <sheet name="Multiplicación" sheetId="2" r:id="rId2"/>
+    <sheet name="Descuentos" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja5" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -67,7 +73,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
@@ -102,7 +108,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9dc3e6"/>
+        <fgColor rgb="FF9DC3E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,106 +147,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="31">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="22" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -251,10 +248,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -292,71 +289,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -384,7 +381,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -407,11 +404,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -420,13 +417,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -436,7 +433,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -445,7 +442,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -454,7 +451,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -462,10 +459,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -530,24 +527,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="28" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="10.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="29" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="29" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="30" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -557,7 +554,7 @@
       <c r="G1" s="18"/>
       <c r="H1" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="19" t="s">
         <v>5</v>
@@ -579,7 +576,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="23" t="s">
         <v>7</v>
@@ -588,20 +585,22 @@
         <v>10</v>
       </c>
       <c r="D3" s="24">
-        <f>C3*E3</f>
+        <f t="shared" ref="D3:D10" si="0">C3*E3</f>
+        <v>3990</v>
       </c>
       <c r="E3" s="24">
         <v>399</v>
       </c>
       <c r="F3" s="24">
-        <f>D3*$G$3</f>
+        <f t="shared" ref="F3:F10" si="1">D3*$G$3</f>
+        <v>837.9</v>
       </c>
       <c r="G3" s="25">
         <v>0.21</v>
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="23" t="s">
         <v>8</v>
@@ -610,18 +609,20 @@
         <v>5</v>
       </c>
       <c r="D4" s="24">
-        <f>C4*E4</f>
+        <f t="shared" si="0"/>
+        <v>2495</v>
       </c>
       <c r="E4" s="24">
         <v>499</v>
       </c>
       <c r="F4" s="24">
-        <f>D4*$G$3</f>
+        <f t="shared" si="1"/>
+        <v>523.94999999999993</v>
       </c>
       <c r="G4" s="26"/>
       <c r="H4" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="23" t="s">
         <v>9</v>
@@ -630,18 +631,20 @@
         <v>645</v>
       </c>
       <c r="D5" s="24">
-        <f>C5*E5</f>
+        <f t="shared" si="0"/>
+        <v>128355</v>
       </c>
       <c r="E5" s="24">
         <v>199</v>
       </c>
       <c r="F5" s="24">
-        <f>D5*$G$3</f>
+        <f t="shared" si="1"/>
+        <v>26954.55</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="27"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="23" t="s">
         <v>10</v>
@@ -650,18 +653,20 @@
         <v>54</v>
       </c>
       <c r="D6" s="24">
-        <f>C6*E6</f>
+        <f t="shared" si="0"/>
+        <v>5346</v>
       </c>
       <c r="E6" s="24">
         <v>99</v>
       </c>
       <c r="F6" s="24">
-        <f>D6*$G$3</f>
+        <f t="shared" si="1"/>
+        <v>1122.6599999999999</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="23" t="s">
         <v>11</v>
@@ -670,18 +675,20 @@
         <v>21</v>
       </c>
       <c r="D7" s="24">
-        <f>C7*E7</f>
+        <f t="shared" si="0"/>
+        <v>1428</v>
       </c>
       <c r="E7" s="24">
         <v>68</v>
       </c>
       <c r="F7" s="24">
-        <f>D7*$G$3</f>
+        <f t="shared" si="1"/>
+        <v>299.88</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="23" t="s">
         <v>12</v>
@@ -690,18 +697,20 @@
         <v>44</v>
       </c>
       <c r="D8" s="24">
-        <f>C8*E8</f>
+        <f t="shared" si="0"/>
+        <v>28600</v>
       </c>
       <c r="E8" s="24">
         <v>650</v>
       </c>
       <c r="F8" s="24">
-        <f>D8*$G$3</f>
+        <f t="shared" si="1"/>
+        <v>6006</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="23" t="s">
         <v>13</v>
@@ -710,18 +719,20 @@
         <v>65</v>
       </c>
       <c r="D9" s="24">
-        <f>C9*E9</f>
+        <f t="shared" si="0"/>
+        <v>1300</v>
       </c>
       <c r="E9" s="24">
         <v>20</v>
       </c>
       <c r="F9" s="24">
-        <f>D9*$G$3</f>
+        <f t="shared" si="1"/>
+        <v>273</v>
       </c>
       <c r="G9" s="26"/>
       <c r="H9" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="23" t="s">
         <v>14</v>
@@ -730,13 +741,15 @@
         <v>45</v>
       </c>
       <c r="D10" s="24">
-        <f>C10*E10</f>
+        <f t="shared" si="0"/>
+        <v>1305</v>
       </c>
       <c r="E10" s="24">
         <v>29</v>
       </c>
       <c r="F10" s="24">
-        <f>D10*$G$3</f>
+        <f t="shared" si="1"/>
+        <v>274.05</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="4"/>
@@ -747,27 +760,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="7.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="7.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="13.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="13">
         <v>1</v>
@@ -800,354 +805,454 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="13">
         <f>$A2*$B1</f>
+        <v>1</v>
       </c>
       <c r="C2" s="13">
         <f>$A2*$C1</f>
+        <v>2</v>
       </c>
       <c r="D2" s="13">
         <f>$A2*$D1</f>
+        <v>3</v>
       </c>
       <c r="E2" s="13">
         <f>$A2*$E1</f>
+        <v>4</v>
       </c>
       <c r="F2" s="13">
         <f>$A2*$F1</f>
+        <v>5</v>
       </c>
       <c r="G2" s="13">
         <f>$A2*$G1</f>
+        <v>6</v>
       </c>
       <c r="H2" s="13">
         <f>$A2*$H1</f>
+        <v>7</v>
       </c>
       <c r="I2" s="13">
         <f>$A2*$I1</f>
+        <v>8</v>
       </c>
       <c r="J2" s="13">
         <f>$A2*$J1</f>
+        <v>9</v>
       </c>
       <c r="K2" s="13">
         <f>$A2*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="13">
         <f>$A3*$B1</f>
+        <v>2</v>
       </c>
       <c r="C3" s="13">
         <f>$A3*$C1</f>
+        <v>4</v>
       </c>
       <c r="D3" s="13">
         <f>$A3*$D1</f>
+        <v>6</v>
       </c>
       <c r="E3" s="13">
         <f>$A3*$E1</f>
+        <v>8</v>
       </c>
       <c r="F3" s="13">
         <f>$A3*$F1</f>
+        <v>10</v>
       </c>
       <c r="G3" s="13">
         <f>$A3*$G1</f>
+        <v>12</v>
       </c>
       <c r="H3" s="13">
         <f>$A3*$H1</f>
+        <v>14</v>
       </c>
       <c r="I3" s="13">
         <f>$A3*$I1</f>
+        <v>16</v>
       </c>
       <c r="J3" s="13">
         <f>$A3*$J1</f>
+        <v>18</v>
       </c>
       <c r="K3" s="13">
         <f>$A3*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="13">
         <f>$A4*$B1</f>
+        <v>3</v>
       </c>
       <c r="C4" s="13">
         <f>$A4*$C1</f>
+        <v>6</v>
       </c>
       <c r="D4" s="13">
         <f>$A4*$D1</f>
+        <v>9</v>
       </c>
       <c r="E4" s="13">
         <f>$A4*$E1</f>
+        <v>12</v>
       </c>
       <c r="F4" s="13">
         <f>$A4*$F1</f>
+        <v>15</v>
       </c>
       <c r="G4" s="13">
         <f>$A4*$G1</f>
+        <v>18</v>
       </c>
       <c r="H4" s="13">
         <f>$A4*$H1</f>
+        <v>21</v>
       </c>
       <c r="I4" s="13">
         <f>$A4*$I1</f>
+        <v>24</v>
       </c>
       <c r="J4" s="13">
         <f>$A4*$J1</f>
+        <v>27</v>
       </c>
       <c r="K4" s="13">
         <f>$A4*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
       <c r="B5" s="13">
         <f>$A5*$B1</f>
+        <v>4</v>
       </c>
       <c r="C5" s="13">
         <f>$A5*$C1</f>
+        <v>8</v>
       </c>
       <c r="D5" s="13">
         <f>$A5*$D1</f>
+        <v>12</v>
       </c>
       <c r="E5" s="13">
         <f>$A5*$E1</f>
+        <v>16</v>
       </c>
       <c r="F5" s="13">
         <f>$A5*$F1</f>
+        <v>20</v>
       </c>
       <c r="G5" s="13">
         <f>$A5*$G1</f>
+        <v>24</v>
       </c>
       <c r="H5" s="13">
         <f>$A5*$H1</f>
+        <v>28</v>
       </c>
       <c r="I5" s="13">
         <f>$A5*$I1</f>
+        <v>32</v>
       </c>
       <c r="J5" s="13">
         <f>$A5*$J1</f>
+        <v>36</v>
       </c>
       <c r="K5" s="13">
         <f>$A5*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
       <c r="B6" s="13">
         <f>$A6*$B1</f>
+        <v>5</v>
       </c>
       <c r="C6" s="13">
         <f>$A6*$C1</f>
+        <v>10</v>
       </c>
       <c r="D6" s="13">
         <f>$A6*$D1</f>
+        <v>15</v>
       </c>
       <c r="E6" s="13">
         <f>$A6*$E1</f>
+        <v>20</v>
       </c>
       <c r="F6" s="13">
         <f>$A6*$F1</f>
+        <v>25</v>
       </c>
       <c r="G6" s="13">
         <f>$A6*$G1</f>
+        <v>30</v>
       </c>
       <c r="H6" s="13">
         <f>$A6*$H1</f>
+        <v>35</v>
       </c>
       <c r="I6" s="13">
         <f>$A6*$I1</f>
+        <v>40</v>
       </c>
       <c r="J6" s="13">
         <f>$A6*$J1</f>
+        <v>45</v>
       </c>
       <c r="K6" s="13">
         <f>$A6*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
       <c r="B7" s="13">
         <f>$A7*$B1</f>
+        <v>6</v>
       </c>
       <c r="C7" s="13">
         <f>$A7*$C1</f>
+        <v>12</v>
       </c>
       <c r="D7" s="13">
         <f>$A7*$D1</f>
+        <v>18</v>
       </c>
       <c r="E7" s="13">
         <f>$A7*$E1</f>
+        <v>24</v>
       </c>
       <c r="F7" s="13">
         <f>$A7*$F1</f>
+        <v>30</v>
       </c>
       <c r="G7" s="13">
         <f>$A7*$G1</f>
+        <v>36</v>
       </c>
       <c r="H7" s="13">
         <f>$A7*$H1</f>
+        <v>42</v>
       </c>
       <c r="I7" s="13">
         <f>$A7*$I1</f>
+        <v>48</v>
       </c>
       <c r="J7" s="13">
         <f>$A7*$J1</f>
+        <v>54</v>
       </c>
       <c r="K7" s="13">
         <f>$A7*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>7</v>
       </c>
       <c r="B8" s="13">
         <f>$A8*$B1</f>
+        <v>7</v>
       </c>
       <c r="C8" s="13">
         <f>$A8*$C1</f>
+        <v>14</v>
       </c>
       <c r="D8" s="13">
         <f>$A8*$D1</f>
+        <v>21</v>
       </c>
       <c r="E8" s="13">
         <f>$A8*$E1</f>
+        <v>28</v>
       </c>
       <c r="F8" s="13">
         <f>$A8*$F1</f>
+        <v>35</v>
       </c>
       <c r="G8" s="13">
         <f>$A8*$G1</f>
+        <v>42</v>
       </c>
       <c r="H8" s="13">
         <f>$A8*$H1</f>
+        <v>49</v>
       </c>
       <c r="I8" s="13">
         <f>$A8*$I1</f>
+        <v>56</v>
       </c>
       <c r="J8" s="13">
         <f>$A8*$J1</f>
+        <v>63</v>
       </c>
       <c r="K8" s="13">
         <f>$A8*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
       <c r="B9" s="13">
         <f>$A9*$B1</f>
+        <v>8</v>
       </c>
       <c r="C9" s="13">
         <f>$A9*$C1</f>
+        <v>16</v>
       </c>
       <c r="D9" s="13">
         <f>$A9*$D1</f>
+        <v>24</v>
       </c>
       <c r="E9" s="13">
         <f>$A9*$E1</f>
+        <v>32</v>
       </c>
       <c r="F9" s="13">
         <f>$A9*$F1</f>
+        <v>40</v>
       </c>
       <c r="G9" s="13">
         <f>$A9*$G1</f>
+        <v>48</v>
       </c>
       <c r="H9" s="13">
         <f>$A9*$H1</f>
+        <v>56</v>
       </c>
       <c r="I9" s="13">
         <f>$A9*$I1</f>
+        <v>64</v>
       </c>
       <c r="J9" s="13">
         <f>$A9*$J1</f>
+        <v>72</v>
       </c>
       <c r="K9" s="13">
         <f>$A9*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
       <c r="B10" s="13">
         <f>$A10*$B1</f>
+        <v>9</v>
       </c>
       <c r="C10" s="13">
         <f>$A10*$C1</f>
+        <v>18</v>
       </c>
       <c r="D10" s="13">
         <f>$A10*$D1</f>
+        <v>27</v>
       </c>
       <c r="E10" s="13">
         <f>$A10*$E1</f>
+        <v>36</v>
       </c>
       <c r="F10" s="13">
         <f>$A10*$F1</f>
+        <v>45</v>
       </c>
       <c r="G10" s="13">
         <f>$A10*$G1</f>
+        <v>54</v>
       </c>
       <c r="H10" s="13">
         <f>$A10*$H1</f>
+        <v>63</v>
       </c>
       <c r="I10" s="13">
         <f>$A10*$I1</f>
+        <v>72</v>
       </c>
       <c r="J10" s="13">
         <f>$A10*$J1</f>
+        <v>81</v>
       </c>
       <c r="K10" s="13">
         <f>$A10*$K1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
       <c r="B11" s="13">
         <f>$A11*$B1</f>
+        <v>10</v>
       </c>
       <c r="C11" s="13">
         <f>$A11*$C1</f>
+        <v>20</v>
       </c>
       <c r="D11" s="13">
         <f>$A11*$D1</f>
+        <v>30</v>
       </c>
       <c r="E11" s="13">
         <f>$A11*$E1</f>
+        <v>40</v>
       </c>
       <c r="F11" s="13">
         <f>$A11*$F1</f>
+        <v>50</v>
       </c>
       <c r="G11" s="13">
         <f>$A11*$G1</f>
+        <v>60</v>
       </c>
       <c r="H11" s="13">
         <f>$A11*$H1</f>
+        <v>70</v>
       </c>
       <c r="I11" s="13">
         <f>$A11*$I1</f>
+        <v>80</v>
       </c>
       <c r="J11" s="13">
         <f>$A11*$J1</f>
+        <v>90</v>
       </c>
       <c r="K11" s="13">
         <f>$A11*$K1</f>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1156,35 +1261,35 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
         <v>0</v>
@@ -1195,14 +1300,14 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
         <v>1</v>
@@ -1217,7 +1322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="8">
         <v>1</v>
@@ -1227,12 +1332,14 @@
       </c>
       <c r="D6" s="2">
         <f>B6*C6</f>
+        <v>120</v>
       </c>
       <c r="E6" s="2">
         <f>D6-(D6*$C$3)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+        <v>105.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="8">
         <v>2</v>
@@ -1242,12 +1349,14 @@
       </c>
       <c r="D7" s="2">
         <f>B7*C7</f>
+        <v>280</v>
       </c>
       <c r="E7" s="2">
         <f>D7-(D7*$C$3)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+        <v>246.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="8">
         <v>3</v>
@@ -1257,12 +1366,14 @@
       </c>
       <c r="D8" s="2">
         <f>B8*C8</f>
+        <v>480</v>
       </c>
       <c r="E8" s="2">
         <f>D8-(D8*$C$3)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+        <v>422.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="8">
         <v>4</v>
@@ -1272,12 +1383,14 @@
       </c>
       <c r="D9" s="2">
         <f>B9*C9</f>
+        <v>720</v>
       </c>
       <c r="E9" s="2">
         <f>D10-(D10*$C$3)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="8">
         <v>5</v>
@@ -1287,19 +1400,21 @@
       </c>
       <c r="D10" s="2">
         <f>B10*C10</f>
+        <v>1000</v>
       </c>
       <c r="E10" s="2">
         <f>D11-(D11*$C$3)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="9"/>
@@ -1312,25 +1427,26 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
-        <f>NOW()</f>
-        <v>25569.041666666668</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+        <f ca="1">NOW()</f>
+        <v>45567.370307754631</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <f>PI()</f>
+        <v>3.1415926535897931</v>
       </c>
     </row>
   </sheetData>
